--- a/DEVELOPMENT_ALL_OLD_NEW/COLINSLOFT/CS.0227 - TOUCH DARK BLUE WASH.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/COLINSLOFT/CS.0227 - TOUCH DARK BLUE WASH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\COLINSLOFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BAF166-B4D7-4272-9598-65FFD71D6B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782D0BF7-5F10-4CE1-842D-39F4019E196A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="mühendisler">[1]Sayfa6!$A$2:$A$10</definedName>
     <definedName name="Müşteriler">[1]Sayfa6!$B$2:$B$20</definedName>
     <definedName name="NEW">[2]DATA!$C$2:$C$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$52</definedName>
     <definedName name="SUPERVISOR">[2]DATA!$B$2:$B$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
   <si>
     <t>dcr</t>
   </si>
@@ -1573,7 +1573,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="294">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2017,53 +2017,299 @@
     <xf numFmtId="164" fontId="8" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2077,12 +2323,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -2173,308 +2413,98 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="56" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="54" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="65" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="65" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3099,7 +3129,7 @@
   <sheetPr codeName="Sayfa3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="5" customWidth="1"/>
@@ -3894,21 +3924,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="175">
+      <c r="C2" s="248">
         <v>46268</v>
       </c>
-      <c r="D2" s="176"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="175" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="248" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="176"/>
-      <c r="H2" s="178" t="s">
+      <c r="G2" s="249"/>
+      <c r="H2" s="251" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="179"/>
-      <c r="J2" s="179"/>
-      <c r="K2" s="180"/>
+      <c r="I2" s="252"/>
+      <c r="J2" s="252"/>
+      <c r="K2" s="253"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3917,17 +3947,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="175" t="s">
+      <c r="C3" s="248" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="176"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="187" t="s">
+      <c r="D3" s="249"/>
+      <c r="E3" s="250"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="260" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="188"/>
+      <c r="I3" s="261"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3941,17 +3971,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="262" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="266"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3960,17 +3990,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="267">
         <v>60552622</v>
       </c>
-      <c r="D5" s="195"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="174"/>
+      <c r="D5" s="268"/>
+      <c r="E5" s="269"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="235"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3979,17 +4009,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="197" t="s">
+      <c r="C6" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="198"/>
-      <c r="E6" s="199"/>
-      <c r="F6" s="183"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="173"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="174"/>
+      <c r="D6" s="271"/>
+      <c r="E6" s="272"/>
+      <c r="F6" s="256"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="234"/>
+      <c r="I6" s="235"/>
+      <c r="J6" s="234"/>
+      <c r="K6" s="235"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3998,17 +4028,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="170" t="s">
+      <c r="C7" s="245" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="171"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="184"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="174"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="174"/>
+      <c r="D7" s="246"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="256"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="234"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="234"/>
+      <c r="K7" s="235"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -4017,15 +4047,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="200"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="202"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="184"/>
+      <c r="C8" s="242"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="244"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="257"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="173"/>
-      <c r="K8" s="174"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="235"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -4034,17 +4064,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="239">
         <v>4</v>
       </c>
-      <c r="D9" s="204"/>
-      <c r="E9" s="205"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="184"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="257"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="174"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="235"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -4053,15 +4083,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="203"/>
-      <c r="D10" s="204"/>
-      <c r="E10" s="205"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="184"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="257"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="173"/>
-      <c r="K10" s="174"/>
+      <c r="J10" s="234"/>
+      <c r="K10" s="235"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -4070,15 +4100,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="206"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="184"/>
-      <c r="H11" s="173"/>
-      <c r="I11" s="174"/>
-      <c r="J11" s="173"/>
-      <c r="K11" s="174"/>
+      <c r="C11" s="236"/>
+      <c r="D11" s="237"/>
+      <c r="E11" s="238"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="235"/>
+      <c r="J11" s="234"/>
+      <c r="K11" s="235"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -4087,17 +4117,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="209" t="s">
+      <c r="C12" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="210"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="183"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="173"/>
-      <c r="K12" s="174"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="256"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="234"/>
+      <c r="I12" s="235"/>
+      <c r="J12" s="234"/>
+      <c r="K12" s="235"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -4106,15 +4136,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="206"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="185"/>
-      <c r="G13" s="186"/>
-      <c r="H13" s="173"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="173"/>
-      <c r="K13" s="174"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="238"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="259"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="235"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4123,17 +4153,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="214" t="s">
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="219" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="215"/>
-      <c r="H14" s="218" t="s">
+      <c r="G14" s="220"/>
+      <c r="H14" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="219"/>
+      <c r="I14" s="224"/>
       <c r="J14" s="16"/>
       <c r="K14" s="17"/>
       <c r="L14" s="4"/>
@@ -4151,14 +4181,14 @@
       <c r="E15" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="216"/>
-      <c r="G15" s="217"/>
-      <c r="H15" s="216"/>
-      <c r="I15" s="220"/>
-      <c r="J15" s="221" t="s">
+      <c r="F15" s="221"/>
+      <c r="G15" s="222"/>
+      <c r="H15" s="221"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="223" t="s">
+      <c r="K15" s="228" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -4184,12 +4214,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="225" t="s">
+      <c r="H16" s="230" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="225"/>
-      <c r="J16" s="222"/>
-      <c r="K16" s="224"/>
+      <c r="I16" s="230"/>
+      <c r="J16" s="227"/>
+      <c r="K16" s="229"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -4198,15 +4228,15 @@
       <c r="B17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="226" t="s">
+      <c r="C17" s="208" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="227"/>
-      <c r="E17" s="227"/>
-      <c r="F17" s="227"/>
-      <c r="G17" s="227"/>
-      <c r="H17" s="227"/>
-      <c r="I17" s="228"/>
+      <c r="D17" s="209"/>
+      <c r="E17" s="209"/>
+      <c r="F17" s="209"/>
+      <c r="G17" s="209"/>
+      <c r="H17" s="209"/>
+      <c r="I17" s="210"/>
       <c r="J17" s="28"/>
       <c r="K17" s="29"/>
       <c r="L17" s="25"/>
@@ -4231,16 +4261,16 @@
     </row>
     <row r="19" spans="1:13" ht="98.1" customHeight="1">
       <c r="A19" s="26"/>
-      <c r="B19" s="291" t="s">
+      <c r="B19" s="165" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="292"/>
+      <c r="C19" s="166"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
-      <c r="I19" s="293"/>
+      <c r="I19" s="167"/>
       <c r="J19" s="46"/>
       <c r="K19" s="42"/>
       <c r="L19" s="25"/>
@@ -4249,13 +4279,13 @@
     <row r="20" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A20" s="26"/>
       <c r="B20" s="92"/>
-      <c r="C20" s="229"/>
-      <c r="D20" s="230"/>
-      <c r="E20" s="230"/>
-      <c r="F20" s="230"/>
-      <c r="G20" s="230"/>
-      <c r="H20" s="230"/>
-      <c r="I20" s="231"/>
+      <c r="C20" s="211"/>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="212"/>
+      <c r="G20" s="212"/>
+      <c r="H20" s="212"/>
+      <c r="I20" s="213"/>
       <c r="J20" s="93"/>
       <c r="K20" s="94"/>
       <c r="L20" s="25"/>
@@ -4281,10 +4311,10 @@
       <c r="G21" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="232" t="s">
+      <c r="H21" s="214" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="233"/>
+      <c r="I21" s="215"/>
       <c r="J21" s="100"/>
       <c r="K21" s="101"/>
       <c r="L21" s="25"/>
@@ -4329,10 +4359,10 @@
       <c r="G23" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="232" t="s">
+      <c r="H23" s="214" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="233"/>
+      <c r="I23" s="215"/>
       <c r="J23" s="100"/>
       <c r="K23" s="101"/>
       <c r="L23" s="25"/>
@@ -4346,8 +4376,8 @@
       <c r="E24" s="105"/>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
-      <c r="H24" s="234"/>
-      <c r="I24" s="234"/>
+      <c r="H24" s="216"/>
+      <c r="I24" s="216"/>
       <c r="J24" s="107"/>
       <c r="K24" s="107"/>
       <c r="L24" s="25"/>
@@ -4373,10 +4403,10 @@
       <c r="G25" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="236" t="s">
+      <c r="H25" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="236"/>
+      <c r="I25" s="201"/>
       <c r="J25" s="111"/>
       <c r="K25" s="111"/>
       <c r="L25" s="25"/>
@@ -4394,10 +4424,10 @@
       <c r="G26" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="237" t="s">
+      <c r="H26" s="202" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="237"/>
+      <c r="I26" s="202"/>
       <c r="J26" s="111"/>
       <c r="K26" s="111"/>
       <c r="L26" s="25"/>
@@ -4415,10 +4445,10 @@
       <c r="G27" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="H27" s="241" t="s">
+      <c r="H27" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="242"/>
+      <c r="I27" s="207"/>
       <c r="J27" s="111"/>
       <c r="K27" s="111"/>
       <c r="L27" s="25"/>
@@ -4444,58 +4474,54 @@
       <c r="G28" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="238" t="s">
+      <c r="H28" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="I28" s="238"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="111"/>
       <c r="K28" s="111"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
     </row>
-    <row r="29" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="29" spans="1:13" ht="73.8" customHeight="1">
       <c r="A29" s="26"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="161" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="162"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="162"/>
-      <c r="G29" s="163"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="118"/>
-      <c r="J29" s="107"/>
-      <c r="K29" s="119"/>
+      <c r="B29" s="294" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="295"/>
+      <c r="D29" s="296"/>
+      <c r="E29" s="297"/>
+      <c r="F29" s="298"/>
+      <c r="G29" s="299"/>
+      <c r="H29" s="300"/>
+      <c r="I29" s="301"/>
+      <c r="J29" s="302"/>
+      <c r="K29" s="303"/>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
     </row>
     <row r="30" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A30" s="26"/>
-      <c r="B30" s="108" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="120">
-        <v>5</v>
-      </c>
-      <c r="G30" s="121" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="164" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" s="164"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="120"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="273" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="274"/>
+      <c r="E30" s="274"/>
+      <c r="F30" s="274"/>
+      <c r="G30" s="275"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="119"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A31" s="26"/>
-      <c r="B31" s="108"/>
+      <c r="B31" s="108" t="s">
+        <v>50</v>
+      </c>
       <c r="C31" s="96"/>
       <c r="D31" s="96"/>
       <c r="E31" s="96"/>
@@ -4505,10 +4531,10 @@
       <c r="G31" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="164" t="s">
-        <v>69</v>
-      </c>
-      <c r="I31" s="164"/>
+      <c r="H31" s="198" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="198"/>
       <c r="J31" s="120"/>
       <c r="K31" s="120"/>
       <c r="L31" s="25"/>
@@ -4516,20 +4542,20 @@
     </row>
     <row r="32" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A32" s="26"/>
-      <c r="B32" s="122"/>
+      <c r="B32" s="108"/>
       <c r="C32" s="96"/>
       <c r="D32" s="96"/>
       <c r="E32" s="96"/>
       <c r="F32" s="120">
-        <v>900</v>
+        <v>5</v>
       </c>
       <c r="G32" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="164" t="s">
-        <v>52</v>
-      </c>
-      <c r="I32" s="164"/>
+      <c r="H32" s="198" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="198"/>
       <c r="J32" s="120"/>
       <c r="K32" s="120"/>
       <c r="L32" s="25"/>
@@ -4537,215 +4563,215 @@
     </row>
     <row r="33" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A33" s="26"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="126"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="107"/>
+      <c r="B33" s="122"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="120">
+        <v>900</v>
+      </c>
+      <c r="G33" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="198" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="198"/>
+      <c r="J33" s="120"/>
+      <c r="K33" s="120"/>
       <c r="L33" s="25"/>
       <c r="M33" s="25"/>
     </row>
     <row r="34" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A34" s="26"/>
-      <c r="B34" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="96">
-        <v>3</v>
-      </c>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96">
-        <v>100</v>
-      </c>
-      <c r="F34" s="120">
-        <v>2</v>
-      </c>
-      <c r="G34" s="128" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" s="239" t="s">
-        <v>54</v>
-      </c>
-      <c r="I34" s="240"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="101"/>
+      <c r="B34" s="123"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="107"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="126"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="107"/>
+      <c r="K34" s="107"/>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
     </row>
     <row r="35" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A35" s="26"/>
-      <c r="B35" s="129" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="130">
+      <c r="B35" s="108" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="96">
+        <v>3</v>
+      </c>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96">
+        <v>100</v>
+      </c>
+      <c r="F35" s="120">
         <v>2</v>
       </c>
-      <c r="D35" s="131" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="130">
-        <v>120</v>
-      </c>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="164"/>
-      <c r="I35" s="164"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="G35" s="128" t="s">
+        <v>37</v>
+      </c>
+      <c r="H35" s="204" t="s">
+        <v>54</v>
+      </c>
+      <c r="I35" s="205"/>
+      <c r="J35" s="101"/>
+      <c r="K35" s="101"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
     </row>
     <row r="36" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A36" s="26"/>
-      <c r="B36" s="283"/>
-      <c r="C36" s="284"/>
-      <c r="D36" s="285"/>
-      <c r="E36" s="284"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="286"/>
-      <c r="I36" s="287"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="288"/>
+      <c r="B36" s="129" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="130">
+        <v>2</v>
+      </c>
+      <c r="D36" s="131" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="130">
+        <v>120</v>
+      </c>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="198"/>
+      <c r="I36" s="198"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
       <c r="L36" s="25"/>
       <c r="M36" s="25"/>
     </row>
     <row r="37" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A37" s="26"/>
-      <c r="B37" s="278" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="279">
-        <v>5</v>
-      </c>
-      <c r="D37" s="65">
-        <v>40</v>
-      </c>
-      <c r="E37" s="279">
-        <v>100</v>
-      </c>
-      <c r="F37" s="38">
-        <v>1</v>
-      </c>
-      <c r="G37" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="280" t="s">
-        <v>67</v>
-      </c>
-      <c r="I37" s="281"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="282"/>
+      <c r="B37" s="159"/>
+      <c r="C37" s="160"/>
+      <c r="D37" s="161"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="163"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="164"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
     </row>
     <row r="38" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A38" s="26"/>
-      <c r="B38" s="278"/>
-      <c r="C38" s="279"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="279"/>
+      <c r="B38" s="154" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="155">
+        <v>5</v>
+      </c>
+      <c r="D38" s="65">
+        <v>40</v>
+      </c>
+      <c r="E38" s="155">
+        <v>100</v>
+      </c>
       <c r="F38" s="38">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="H38" s="289" t="s">
-        <v>68</v>
-      </c>
-      <c r="I38" s="290"/>
+        <v>45</v>
+      </c>
+      <c r="H38" s="156" t="s">
+        <v>67</v>
+      </c>
+      <c r="I38" s="157"/>
       <c r="J38" s="49"/>
-      <c r="K38" s="282"/>
+      <c r="K38" s="158"/>
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
     </row>
     <row r="39" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A39" s="26"/>
-      <c r="B39" s="108" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="96">
-        <v>2</v>
-      </c>
-      <c r="D39" s="96" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="279"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="280"/>
-      <c r="I39" s="281"/>
+      <c r="B39" s="154"/>
+      <c r="C39" s="155"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="155"/>
+      <c r="F39" s="38">
+        <v>100</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="284" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="285"/>
       <c r="J39" s="49"/>
-      <c r="K39" s="282"/>
+      <c r="K39" s="158"/>
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
     </row>
     <row r="40" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A40" s="26"/>
-      <c r="B40" s="116"/>
-      <c r="C40" s="124"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="107"/>
-      <c r="G40" s="107"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="107"/>
-      <c r="K40" s="119"/>
+      <c r="B40" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="96">
+        <v>2</v>
+      </c>
+      <c r="D40" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="155"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="157"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="158"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
     </row>
     <row r="41" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A41" s="26"/>
-      <c r="B41" s="132" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="131">
-        <v>5</v>
-      </c>
-      <c r="D41" s="131">
-        <v>45</v>
-      </c>
-      <c r="E41" s="131">
-        <v>100</v>
-      </c>
-      <c r="F41" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="G41" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H41" s="243" t="s">
-        <v>56</v>
-      </c>
-      <c r="I41" s="243"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
+      <c r="B41" s="116"/>
+      <c r="C41" s="124"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="117"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="107"/>
+      <c r="K41" s="119"/>
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
     </row>
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
-      <c r="B42" s="132"/>
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
+      <c r="B42" s="132" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="131">
+        <v>5</v>
+      </c>
+      <c r="D42" s="131">
+        <v>45</v>
+      </c>
+      <c r="E42" s="131">
+        <v>100</v>
+      </c>
       <c r="F42" s="34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G42" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="H42" s="244" t="s">
-        <v>57</v>
-      </c>
-      <c r="I42" s="244"/>
+      <c r="H42" s="281" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="281"/>
       <c r="J42" s="34"/>
       <c r="K42" s="34"/>
       <c r="L42" s="25"/>
@@ -4753,85 +4779,85 @@
     </row>
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="26"/>
-      <c r="B43" s="108" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="96">
-        <v>2</v>
-      </c>
-      <c r="D43" s="96" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="96"/>
-      <c r="F43" s="101"/>
-      <c r="G43" s="101"/>
-      <c r="H43" s="245"/>
-      <c r="I43" s="245"/>
-      <c r="J43" s="101"/>
-      <c r="K43" s="101"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="131"/>
+      <c r="D43" s="131"/>
+      <c r="E43" s="131"/>
+      <c r="F43" s="34">
+        <v>1</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" s="282" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="282"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
       <c r="L43" s="25"/>
       <c r="M43" s="25"/>
     </row>
     <row r="44" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A44" s="26"/>
-      <c r="B44" s="116"/>
-      <c r="C44" s="165"/>
-      <c r="D44" s="166"/>
-      <c r="E44" s="166"/>
-      <c r="F44" s="166"/>
-      <c r="G44" s="167"/>
-      <c r="H44" s="168"/>
-      <c r="I44" s="169"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="133"/>
+      <c r="B44" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="96">
+        <v>2</v>
+      </c>
+      <c r="D44" s="96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="96"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="283"/>
+      <c r="I44" s="283"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="101"/>
       <c r="L44" s="25"/>
       <c r="M44" s="25"/>
     </row>
     <row r="45" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A45" s="26"/>
-      <c r="B45" s="134" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="135">
-        <v>5</v>
-      </c>
-      <c r="D45" s="135">
-        <v>45</v>
-      </c>
-      <c r="E45" s="135">
-        <v>100</v>
-      </c>
-      <c r="F45" s="136">
-        <v>3</v>
-      </c>
-      <c r="G45" s="120" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="159" t="s">
-        <v>65</v>
-      </c>
-      <c r="I45" s="160"/>
-      <c r="J45" s="136"/>
-      <c r="K45" s="138"/>
+      <c r="B45" s="116"/>
+      <c r="C45" s="276"/>
+      <c r="D45" s="277"/>
+      <c r="E45" s="277"/>
+      <c r="F45" s="277"/>
+      <c r="G45" s="278"/>
+      <c r="H45" s="279"/>
+      <c r="I45" s="280"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="133"/>
       <c r="L45" s="25"/>
       <c r="M45" s="25"/>
     </row>
     <row r="46" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A46" s="26"/>
       <c r="B46" s="134" t="s">
-        <v>39</v>
-      </c>
-      <c r="C46" s="135"/>
-      <c r="D46" s="135"/>
-      <c r="E46" s="135"/>
-      <c r="F46" s="136"/>
+        <v>62</v>
+      </c>
+      <c r="C46" s="135">
+        <v>5</v>
+      </c>
+      <c r="D46" s="135">
+        <v>45</v>
+      </c>
+      <c r="E46" s="135">
+        <v>100</v>
+      </c>
+      <c r="F46" s="136">
+        <v>3</v>
+      </c>
       <c r="G46" s="120" t="s">
-        <v>37</v>
-      </c>
-      <c r="H46" s="137" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="139"/>
+        <v>63</v>
+      </c>
+      <c r="H46" s="292" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="293"/>
       <c r="J46" s="136"/>
       <c r="K46" s="138"/>
       <c r="L46" s="25"/>
@@ -4839,92 +4865,98 @@
     </row>
     <row r="47" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A47" s="26"/>
-      <c r="B47" s="140"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="235"/>
-      <c r="I47" s="235"/>
-      <c r="J47" s="142"/>
-      <c r="K47" s="142"/>
+      <c r="B47" s="134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="135"/>
+      <c r="D47" s="135"/>
+      <c r="E47" s="135"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="H47" s="137" t="s">
+        <v>64</v>
+      </c>
+      <c r="I47" s="139"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="138"/>
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
     </row>
     <row r="48" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A48" s="26"/>
-      <c r="B48" s="143" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="144">
-        <v>1</v>
-      </c>
-      <c r="D48" s="145" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="145">
-        <v>100</v>
-      </c>
-      <c r="F48" s="146">
-        <v>2</v>
-      </c>
-      <c r="G48" s="121" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="248" t="s">
-        <v>60</v>
-      </c>
-      <c r="I48" s="248"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="147"/>
+      <c r="B48" s="140"/>
+      <c r="C48" s="141"/>
+      <c r="D48" s="286"/>
+      <c r="E48" s="286"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="291"/>
+      <c r="I48" s="291"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="142"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
     </row>
     <row r="49" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A49" s="26"/>
-      <c r="B49" s="112" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="111"/>
-      <c r="E49" s="111"/>
-      <c r="F49" s="148"/>
-      <c r="G49" s="147"/>
-      <c r="H49" s="155"/>
-      <c r="I49" s="155"/>
+      <c r="B49" s="143" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="144">
+        <v>1</v>
+      </c>
+      <c r="D49" s="145" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" s="145">
+        <v>100</v>
+      </c>
+      <c r="F49" s="146">
+        <v>2</v>
+      </c>
+      <c r="G49" s="121" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" s="196" t="s">
+        <v>60</v>
+      </c>
+      <c r="I49" s="196"/>
       <c r="J49" s="111"/>
-      <c r="K49" s="111"/>
+      <c r="K49" s="147"/>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
-      <c r="B50" s="149"/>
-      <c r="C50" s="150"/>
-      <c r="D50" s="150"/>
-      <c r="E50" s="150"/>
-      <c r="F50" s="151"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="249"/>
-      <c r="I50" s="249"/>
-      <c r="J50" s="151"/>
-      <c r="K50" s="151"/>
+      <c r="B50" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="111"/>
+      <c r="F50" s="148"/>
+      <c r="G50" s="147"/>
+      <c r="H50" s="287"/>
+      <c r="I50" s="287"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="111"/>
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
     </row>
     <row r="51" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A51" s="26"/>
-      <c r="B51" s="152"/>
-      <c r="C51" s="101"/>
-      <c r="D51" s="101"/>
-      <c r="E51" s="96"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="121"/>
-      <c r="H51" s="164"/>
-      <c r="I51" s="164"/>
-      <c r="J51" s="120"/>
-      <c r="K51" s="120"/>
+      <c r="B51" s="149"/>
+      <c r="C51" s="150"/>
+      <c r="D51" s="150"/>
+      <c r="E51" s="150"/>
+      <c r="F51" s="151"/>
+      <c r="G51" s="151"/>
+      <c r="H51" s="197"/>
+      <c r="I51" s="197"/>
+      <c r="J51" s="151"/>
+      <c r="K51" s="151"/>
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
     </row>
@@ -4936,8 +4968,8 @@
       <c r="E52" s="96"/>
       <c r="F52" s="120"/>
       <c r="G52" s="121"/>
-      <c r="H52" s="164"/>
-      <c r="I52" s="164"/>
+      <c r="H52" s="198"/>
+      <c r="I52" s="198"/>
       <c r="J52" s="120"/>
       <c r="K52" s="120"/>
       <c r="L52" s="25"/>
@@ -4945,46 +4977,46 @@
     </row>
     <row r="53" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
-      <c r="B53" s="153"/>
-      <c r="C53" s="156"/>
-      <c r="D53" s="157"/>
-      <c r="E53" s="157"/>
-      <c r="F53" s="157"/>
-      <c r="G53" s="158"/>
-      <c r="H53" s="250"/>
-      <c r="I53" s="251"/>
-      <c r="J53" s="92"/>
-      <c r="K53" s="92"/>
+      <c r="B53" s="152"/>
+      <c r="C53" s="101"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="121"/>
+      <c r="H53" s="198"/>
+      <c r="I53" s="198"/>
+      <c r="J53" s="120"/>
+      <c r="K53" s="120"/>
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
     </row>
     <row r="54" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A54" s="26"/>
-      <c r="B54" s="43"/>
-      <c r="C54" s="252"/>
-      <c r="D54" s="253"/>
-      <c r="E54" s="253"/>
-      <c r="F54" s="253"/>
-      <c r="G54" s="254"/>
-      <c r="H54" s="255"/>
-      <c r="I54" s="256"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
+      <c r="B54" s="153"/>
+      <c r="C54" s="288"/>
+      <c r="D54" s="289"/>
+      <c r="E54" s="289"/>
+      <c r="F54" s="289"/>
+      <c r="G54" s="290"/>
+      <c r="H54" s="199"/>
+      <c r="I54" s="200"/>
+      <c r="J54" s="92"/>
+      <c r="K54" s="92"/>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
     </row>
     <row r="55" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A55" s="26"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="257"/>
-      <c r="I55" s="258"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="42"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="186"/>
+      <c r="D55" s="187"/>
+      <c r="E55" s="187"/>
+      <c r="F55" s="187"/>
+      <c r="G55" s="188"/>
+      <c r="H55" s="189"/>
+      <c r="I55" s="190"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
       <c r="L55" s="25"/>
       <c r="M55" s="25"/>
     </row>
@@ -4996,23 +5028,23 @@
       <c r="E56" s="42"/>
       <c r="F56" s="45"/>
       <c r="G56" s="45"/>
-      <c r="H56" s="257"/>
-      <c r="I56" s="259"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="192"/>
       <c r="J56" s="46"/>
       <c r="K56" s="42"/>
       <c r="L56" s="25"/>
       <c r="M56" s="25"/>
     </row>
-    <row r="57" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="57" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A57" s="26"/>
-      <c r="B57" s="47"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="42"/>
       <c r="E57" s="42"/>
       <c r="F57" s="45"/>
       <c r="G57" s="45"/>
-      <c r="H57" s="257"/>
-      <c r="I57" s="259"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="193"/>
       <c r="J57" s="46"/>
       <c r="K57" s="42"/>
       <c r="L57" s="25"/>
@@ -5024,10 +5056,10 @@
       <c r="C58" s="48"/>
       <c r="D58" s="48"/>
       <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="246"/>
-      <c r="I58" s="247"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="191"/>
+      <c r="I58" s="193"/>
       <c r="J58" s="46"/>
       <c r="K58" s="42"/>
       <c r="L58" s="25"/>
@@ -5035,76 +5067,76 @@
     </row>
     <row r="59" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A59" s="26"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="194"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="46"/>
+      <c r="K59" s="42"/>
       <c r="L59" s="25"/>
       <c r="M59" s="25"/>
     </row>
     <row r="60" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A60" s="26"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="261"/>
-      <c r="I60" s="261"/>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="37"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52"/>
       <c r="L60" s="25"/>
       <c r="M60" s="25"/>
     </row>
-    <row r="61" spans="1:13" ht="77.099999999999994" customHeight="1">
+    <row r="61" spans="1:13" ht="71.099999999999994" customHeight="1">
       <c r="A61" s="26"/>
       <c r="B61" s="39"/>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
       <c r="E61" s="40"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="262"/>
-      <c r="I61" s="262"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="175"/>
+      <c r="I61" s="175"/>
       <c r="J61" s="42"/>
       <c r="K61" s="42"/>
       <c r="L61" s="25"/>
       <c r="M61" s="25"/>
     </row>
-    <row r="62" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A62" s="53"/>
-      <c r="B62" s="54"/>
-      <c r="C62" s="55"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="56"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="59"/>
-      <c r="J62" s="60"/>
-      <c r="K62" s="60"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="61"/>
+    <row r="62" spans="1:13" ht="77.099999999999994" customHeight="1">
+      <c r="A62" s="26"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="176"/>
+      <c r="I62" s="176"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
     </row>
     <row r="63" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A63" s="53"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="263"/>
-      <c r="I63" s="263"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
       <c r="L63" s="4"/>
       <c r="M63" s="61"/>
     </row>
@@ -5116,8 +5148,8 @@
       <c r="E64" s="40"/>
       <c r="F64" s="38"/>
       <c r="G64" s="38"/>
-      <c r="H64" s="263"/>
-      <c r="I64" s="263"/>
+      <c r="H64" s="177"/>
+      <c r="I64" s="177"/>
       <c r="J64" s="38"/>
       <c r="K64" s="38"/>
       <c r="L64" s="4"/>
@@ -5125,44 +5157,44 @@
     </row>
     <row r="65" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A65" s="53"/>
-      <c r="B65" s="62"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="264"/>
-      <c r="I65" s="265"/>
-      <c r="J65" s="52"/>
-      <c r="K65" s="63"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="177"/>
+      <c r="I65" s="177"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
       <c r="L65" s="4"/>
       <c r="M65" s="61"/>
     </row>
     <row r="66" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A66" s="53"/>
-      <c r="B66" s="64"/>
-      <c r="C66" s="65"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="49"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="266"/>
-      <c r="I66" s="266"/>
-      <c r="J66" s="49"/>
-      <c r="K66" s="49"/>
+      <c r="B66" s="62"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
+      <c r="H66" s="178"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="52"/>
+      <c r="K66" s="63"/>
       <c r="L66" s="4"/>
       <c r="M66" s="61"/>
     </row>
     <row r="67" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A67" s="53"/>
-      <c r="B67" s="66"/>
+      <c r="B67" s="64"/>
       <c r="C67" s="65"/>
       <c r="D67" s="65"/>
       <c r="E67" s="65"/>
       <c r="F67" s="49"/>
       <c r="G67" s="49"/>
-      <c r="H67" s="267"/>
-      <c r="I67" s="267"/>
+      <c r="H67" s="180"/>
+      <c r="I67" s="180"/>
       <c r="J67" s="49"/>
       <c r="K67" s="49"/>
       <c r="L67" s="4"/>
@@ -5170,46 +5202,46 @@
     </row>
     <row r="68" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A68" s="53"/>
-      <c r="B68" s="39"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="268"/>
-      <c r="I68" s="268"/>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="65"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="65"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="181"/>
+      <c r="I68" s="181"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="4"/>
       <c r="M68" s="61"/>
     </row>
     <row r="69" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A69" s="53"/>
-      <c r="B69" s="62"/>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="52"/>
-      <c r="K69" s="52"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="182"/>
+      <c r="I69" s="182"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
       <c r="L69" s="4"/>
       <c r="M69" s="61"/>
     </row>
     <row r="70" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A70" s="53"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="269"/>
-      <c r="I70" s="270"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="68"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
       <c r="L70" s="4"/>
       <c r="M70" s="61"/>
     </row>
@@ -5221,8 +5253,8 @@
       <c r="E71" s="40"/>
       <c r="F71" s="42"/>
       <c r="G71" s="42"/>
-      <c r="H71" s="269"/>
-      <c r="I71" s="270"/>
+      <c r="H71" s="183"/>
+      <c r="I71" s="184"/>
       <c r="J71" s="42"/>
       <c r="K71" s="42"/>
       <c r="L71" s="4"/>
@@ -5230,138 +5262,138 @@
     </row>
     <row r="72" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A72" s="53"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="69"/>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
-      <c r="F72" s="69"/>
-      <c r="G72" s="69"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="68"/>
-      <c r="J72" s="52"/>
-      <c r="K72" s="52"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="183"/>
+      <c r="I72" s="184"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
       <c r="L72" s="4"/>
       <c r="M72" s="61"/>
     </row>
     <row r="73" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A73" s="53"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="71"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="73"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="271"/>
-      <c r="I73" s="271"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="49"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="69"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="69"/>
+      <c r="G73" s="69"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="68"/>
+      <c r="J73" s="52"/>
+      <c r="K73" s="52"/>
       <c r="L73" s="4"/>
       <c r="M73" s="61"/>
     </row>
     <row r="74" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A74" s="53"/>
       <c r="B74" s="70"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="75"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="260"/>
-      <c r="I74" s="260"/>
+      <c r="C74" s="71"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="72"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="185"/>
+      <c r="I74" s="185"/>
       <c r="J74" s="38"/>
-      <c r="K74" s="38"/>
+      <c r="K74" s="49"/>
       <c r="L74" s="4"/>
       <c r="M74" s="61"/>
     </row>
     <row r="75" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A75" s="53"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="78"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="79"/>
-      <c r="H75" s="274"/>
-      <c r="I75" s="274"/>
-      <c r="J75" s="80"/>
-      <c r="K75" s="80"/>
+      <c r="B75" s="70"/>
+      <c r="C75" s="74"/>
+      <c r="D75" s="74"/>
+      <c r="E75" s="75"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="174"/>
+      <c r="I75" s="174"/>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
       <c r="L75" s="4"/>
       <c r="M75" s="61"/>
     </row>
     <row r="76" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A76" s="53"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="82"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="82"/>
-      <c r="F76" s="82"/>
-      <c r="G76" s="82"/>
-      <c r="H76" s="275"/>
-      <c r="I76" s="276"/>
-      <c r="J76" s="83"/>
-      <c r="K76" s="82"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="78"/>
+      <c r="D76" s="78"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="79"/>
+      <c r="H76" s="170"/>
+      <c r="I76" s="170"/>
+      <c r="J76" s="80"/>
+      <c r="K76" s="80"/>
       <c r="L76" s="4"/>
       <c r="M76" s="61"/>
     </row>
     <row r="77" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A77" s="53"/>
-      <c r="B77" s="84"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="272"/>
-      <c r="I77" s="273"/>
-      <c r="J77" s="85"/>
-      <c r="K77" s="35"/>
+      <c r="B77" s="81"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="171"/>
+      <c r="I77" s="172"/>
+      <c r="J77" s="83"/>
+      <c r="K77" s="82"/>
       <c r="L77" s="4"/>
       <c r="M77" s="61"/>
     </row>
     <row r="78" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A78" s="53"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="42"/>
-      <c r="D78" s="42"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="H78" s="277"/>
-      <c r="I78" s="277"/>
-      <c r="J78" s="86"/>
-      <c r="K78" s="42"/>
+      <c r="B78" s="84"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="168"/>
+      <c r="I78" s="169"/>
+      <c r="J78" s="85"/>
+      <c r="K78" s="35"/>
       <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
+      <c r="M78" s="61"/>
     </row>
     <row r="79" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A79" s="53"/>
-      <c r="B79" s="87"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="272"/>
-      <c r="I79" s="273"/>
-      <c r="J79" s="85"/>
-      <c r="K79" s="88"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="173"/>
+      <c r="I79" s="173"/>
+      <c r="J79" s="86"/>
+      <c r="K79" s="42"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
     </row>
-    <row r="80" spans="1:13" ht="61.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="89"/>
+    <row r="80" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A80" s="53"/>
+      <c r="B80" s="87"/>
       <c r="C80" s="35"/>
       <c r="D80" s="35"/>
       <c r="E80" s="35"/>
       <c r="F80" s="35"/>
       <c r="G80" s="35"/>
-      <c r="H80" s="272"/>
-      <c r="I80" s="273"/>
+      <c r="H80" s="168"/>
+      <c r="I80" s="169"/>
       <c r="J80" s="85"/>
       <c r="K80" s="88"/>
-      <c r="L80" s="90"/>
-      <c r="M80" s="91"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13" ht="61.2">
       <c r="A81" s="4"/>
@@ -5371,8 +5403,8 @@
       <c r="E81" s="35"/>
       <c r="F81" s="35"/>
       <c r="G81" s="35"/>
-      <c r="H81" s="272"/>
-      <c r="I81" s="273"/>
+      <c r="H81" s="168"/>
+      <c r="I81" s="169"/>
       <c r="J81" s="85"/>
       <c r="K81" s="88"/>
       <c r="L81" s="90"/>
@@ -5386,30 +5418,42 @@
       <c r="E82" s="35"/>
       <c r="F82" s="35"/>
       <c r="G82" s="35"/>
-      <c r="H82" s="272"/>
-      <c r="I82" s="273"/>
+      <c r="H82" s="168"/>
+      <c r="I82" s="169"/>
       <c r="J82" s="85"/>
       <c r="K82" s="88"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="L82" s="90"/>
+      <c r="M82" s="91"/>
+    </row>
+    <row r="83" spans="1:13" ht="61.2">
       <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="168"/>
+      <c r="I83" s="169"/>
+      <c r="J83" s="85"/>
+      <c r="K83" s="88"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="4"/>
@@ -5486,76 +5530,26 @@
     <row r="109" spans="1:1">
       <c r="A109" s="4"/>
     </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="H50:I50"/>
     <mergeCell ref="C54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
     <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H39:I39"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -5569,21 +5563,74 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:I44"/>
     <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H59:I59"/>
     <mergeCell ref="H49:I49"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="H81:I81"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
